--- a/docs/design-docs/14_共通部品設計書.xlsx
+++ b/docs/design-docs/14_共通部品設計書.xlsx
@@ -10,7 +10,407 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>共通部品設計書</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-COMMON-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>Tilesレイアウト定義</t>
+  </si>
+  <si>
+    <t>template名</t>
+  </si>
+  <si>
+    <t>継承</t>
+  </si>
+  <si>
+    <t>属性</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>baseLayout</t>
+  </si>
+  <si>
+    <t>(root)</t>
+  </si>
+  <si>
+    <t>header, menu, body, footer</t>
+  </si>
+  <si>
+    <t>全画面共通base</t>
+  </si>
+  <si>
+    <t>masterLayout</t>
+  </si>
+  <si>
+    <t>body=menuLayout</t>
+  </si>
+  <si>
+    <t>マスタ管理用</t>
+  </si>
+  <si>
+    <t>wizardLayout</t>
+  </si>
+  <si>
+    <t>body=wizardContent</t>
+  </si>
+  <si>
+    <t>Wizard面用</t>
+  </si>
+  <si>
+    <t>listLayout</t>
+  </si>
+  <si>
+    <t>body=searchArea+listArea</t>
+  </si>
+  <si>
+    <t>一覧面用</t>
+  </si>
+  <si>
+    <t>inputLayout</t>
+  </si>
+  <si>
+    <t>body=formArea</t>
+  </si>
+  <si>
+    <t>入力面用</t>
+  </si>
+  <si>
+    <t>popupLayout</t>
+  </si>
+  <si>
+    <t>header, body</t>
+  </si>
+  <si>
+    <t>Popup用</t>
+  </si>
+  <si>
+    <t>printLayout</t>
+  </si>
+  <si>
+    <t>body</t>
+  </si>
+  <si>
+    <t>印刷用</t>
+  </si>
+  <si>
+    <t>共通JSPインクルード</t>
+  </si>
+  <si>
+    <t>ファイル名</t>
+  </si>
+  <si>
+    <t>パス</t>
+  </si>
+  <si>
+    <t>役割</t>
+  </si>
+  <si>
+    <t>header.jsp</t>
+  </si>
+  <si>
+    <t>/WEB-INF/jsp/common/</t>
+  </si>
+  <si>
+    <t>title bar, login user表示</t>
+  </si>
+  <si>
+    <t>menu.jsp</t>
+  </si>
+  <si>
+    <t>モジュール別menu link</t>
+  </si>
+  <si>
+    <t>footer.jsp</t>
+  </si>
+  <si>
+    <t>copyright</t>
+  </si>
+  <si>
+    <t>paging.jsp</t>
+  </si>
+  <si>
+    <t>paging共通部品</t>
+  </si>
+  <si>
+    <t>errorMessages.jsp</t>
+  </si>
+  <si>
+    <t>&amp;lt;html:errors/&amp;gt;表示</t>
+  </si>
+  <si>
+    <t>confirmDialog.jsp</t>
+  </si>
+  <si>
+    <t>window.confirm用JS</t>
+  </si>
+  <si>
+    <t>error.jsp</t>
+  </si>
+  <si>
+    <t>isErrorPage=true</t>
+  </si>
+  <si>
+    <t>カスタムタグ</t>
+  </si>
+  <si>
+    <t>tag名</t>
+  </si>
+  <si>
+    <t>TLD</t>
+  </si>
+  <si>
+    <t>Java class</t>
+  </si>
+  <si>
+    <t>機能</t>
+  </si>
+  <si>
+    <t>eqp:treeSelect</t>
+  </si>
+  <si>
+    <t>eqp-tree.tld</t>
+  </si>
+  <si>
+    <t>EqpTreeSelectTag</t>
+  </si>
+  <si>
+    <t>設備tree選択(select)</t>
+  </si>
+  <si>
+    <t>date:picker</t>
+  </si>
+  <si>
+    <t>date-picker.tld</t>
+  </si>
+  <si>
+    <t>DatePickerTag</t>
+  </si>
+  <si>
+    <t>日付入力補助(text+calendar Popup)</t>
+  </si>
+  <si>
+    <t>app:sectionHeader</t>
+  </si>
+  <si>
+    <t>app-common.tld</t>
+  </si>
+  <si>
+    <t>SectionHeaderTag</t>
+  </si>
+  <si>
+    <t>section見出(anchor付)</t>
+  </si>
+  <si>
+    <t>app:statusBadge</t>
+  </si>
+  <si>
+    <t>StatusBadgeTag</t>
+  </si>
+  <si>
+    <t>status badge(色付span)</t>
+  </si>
+  <si>
+    <t>app:inspectionChecklist</t>
+  </si>
+  <si>
+    <t>InspectionChecklistTag</t>
+  </si>
+  <si>
+    <t>点検checklist 3階層table</t>
+  </si>
+  <si>
+    <t>app:indexedRow</t>
+  </si>
+  <si>
+    <t>IndexedRowTag</t>
+  </si>
+  <si>
+    <t>動的行(Indexed Properties反復)</t>
+  </si>
+  <si>
+    <t>app:timeline</t>
+  </si>
+  <si>
+    <t>TimelineTag</t>
+  </si>
+  <si>
+    <t>経過記録timeline表示</t>
+  </si>
+  <si>
+    <t>MyBatis Mapper一覧</t>
+  </si>
+  <si>
+    <t>Mapper XML</t>
+  </si>
+  <si>
+    <t>Java Interface</t>
+  </si>
+  <si>
+    <t>担当table</t>
+  </si>
+  <si>
+    <t>EquipmentMapper.xml</t>
+  </si>
+  <si>
+    <t>EqpDao.java</t>
+  </si>
+  <si>
+    <t>equipment</t>
+  </si>
+  <si>
+    <t>InspectionTemplateMapper.xml</t>
+  </si>
+  <si>
+    <t>ChkItemDao.java</t>
+  </si>
+  <si>
+    <t>inspection_template, inspection_items</t>
+  </si>
+  <si>
+    <t>InspectionPlanMapper.xml</t>
+  </si>
+  <si>
+    <t>PlanDao.java</t>
+  </si>
+  <si>
+    <t>inspection_plans</t>
+  </si>
+  <si>
+    <t>InspectionResultMapper.xml</t>
+  </si>
+  <si>
+    <t>ExecDao.java</t>
+  </si>
+  <si>
+    <t>inspection_results, inspection_items_results</t>
+  </si>
+  <si>
+    <t>IncidentMapper.xml</t>
+  </si>
+  <si>
+    <t>IncidentDao.java</t>
+  </si>
+  <si>
+    <t>incidents, incident_timeline, incident_attachments</t>
+  </si>
+  <si>
+    <t>CounterOrderMapper.xml</t>
+  </si>
+  <si>
+    <t>CounterDao.java</t>
+  </si>
+  <si>
+    <t>counter_orders, counter_order_details</t>
+  </si>
+  <si>
+    <t>CapaMapper.xml</t>
+  </si>
+  <si>
+    <t>CapaDao.java</t>
+  </si>
+  <si>
+    <t>capa_reports</t>
+  </si>
+  <si>
+    <t>DeptMapper.xml</t>
+  </si>
+  <si>
+    <t>DeptDao.java</t>
+  </si>
+  <si>
+    <t>departments</t>
+  </si>
+  <si>
+    <t>EmployeeMapper.xml</t>
+  </si>
+  <si>
+    <t>EmpDao.java</t>
+  </si>
+  <si>
+    <t>employees, employee_qualifications</t>
+  </si>
+  <si>
+    <t>CalendarMapper.xml</t>
+  </si>
+  <si>
+    <t>CalendarDao.java</t>
+  </si>
+  <si>
+    <t>holidays</t>
+  </si>
+  <si>
+    <t>PartsMapper.xml</t>
+  </si>
+  <si>
+    <t>PartsDao.java</t>
+  </si>
+  <si>
+    <t>parts, part_equipment_relations, part_usages</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
